--- a/Cronograma_semanal.xlsx
+++ b/Cronograma_semanal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsof\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsof\My_Proyecto\Exodus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66579E4-6DAE-43E9-AD63-9972122272D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66A79C33-3DE2-4802-AA77-8F2EF0280FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>CRONOGRAMA SEMANAL DE ACTIVIDADES</t>
   </si>
@@ -146,6 +146,23 @@
   </si>
   <si>
     <t>ADSO-Analisis y desarrollo de software</t>
+  </si>
+  <si>
+    <t>Refactorización del esquema de la base de datos y actualización de archivos binarios
+- Se actualizó el esquema SQL en `sistema_contable.sql` para incluir nuevas tablas: `aportes`, `deducciones`, `empleados`, `movimientos_inventario`, `nomina`, `novedades`, `parametros`, `permisos`, `productos`, `roles` y `rol_permiso`.
+- Se añadieron claves primarias y restricciones de clave foránea para las nuevas tablas.
+- Se modificó la tabla `usuarios` para incluir los campos `usuario` y `clave_hash`.
+- Se actualizaron las sentencias `INSERT` para la tabla `usuarios`, incluyendo contraseñas cifradas mediante hash.
+- Se actualizaron los archivos binarios en los directorios `__pycache__` de diversos módulos para reflejar los cambios recientes en el código.</t>
+  </si>
+  <si>
+    <t>En consolidacion_service.py Se agregó el campo valor_inventario_inicial a los datos consolidados.
+Esto lo que hace es  que el servicio de equilibrio calcule el cambio de inventario correcto.
+En balance_service.py
+Se cambió la fórmula del flujo de caja de restar compras_inventario (compras totales) a restar cambio_inventario (inventario final - inicial)
+Ahora usa correctamente consolidado['valor_inventario_inicial'] del servicio de consolidación
+El sistema ahora está completo y los tres estados financieros reflejan adecuadamente los datos de los módulos de nómina e inventario.
+ Acabar de explicar. No hay más cambios necesarios a menos que quieras probar con datos históricos que tengan inventario inicial distinto de 0.</t>
   </si>
 </sst>
 </file>
@@ -328,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -354,6 +371,7 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -657,7 +675,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
@@ -668,25 +686,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
@@ -698,11 +716,11 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
       <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
@@ -715,23 +733,23 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
@@ -790,7 +808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="140" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
@@ -800,52 +818,67 @@
       <c r="E10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10" t="s">
+        <v>26</v>
+      </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" ht="371" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>20</v>
-      </c>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="391.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>21</v>
-      </c>
+      <c r="E11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" ht="230" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="371" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="F12" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:9" ht="378" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>

--- a/Cronograma_semanal.xlsx
+++ b/Cronograma_semanal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsof\My_Proyecto\Exodus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66A79C33-3DE2-4802-AA77-8F2EF0280FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76BA01FC-FF94-44D6-A036-5A6CD2A2B36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>CRONOGRAMA SEMANAL DE ACTIVIDADES</t>
   </si>
@@ -163,6 +163,17 @@
 Ahora usa correctamente consolidado['valor_inventario_inicial'] del servicio de consolidación
 El sistema ahora está completo y los tres estados financieros reflejan adecuadamente los datos de los módulos de nómina e inventario.
  Acabar de explicar. No hay más cambios necesarios a menos que quieras probar con datos históricos que tengan inventario inicial distinto de 0.</t>
+  </si>
+  <si>
+    <t>"refactor: unificar entry point en Exodus-login; agregar favicon; corregir import parametros; actualizar SRS
+- Copiar login UI, templates y assets estáticos de Modulo-contable a Exodus-login
+- Reescribir Exodus-login/app.py como entry point principal registrando todos los módulos (auth, contabilidad, inventario, nomina, configuracion)
+- Nuevo routes/auth.py con cookies firmadas (itsdangerous), rate-limit, canonicalización de roles
+- Corregir parametros.py: importar listar_etiquetas desde inventario.modelo
+- Agregar favicon.png + logo en sidebar a templates de Modulo-contable
+- Actualizar readm.md: arquitectura desktop/Tkinter → web/Flask
+- Eliminar Modulo-contable/app.py duplicado
+- Corregir db.py manejo de conexión (id_usuario vs id)"</t>
   </si>
 </sst>
 </file>
@@ -172,7 +183,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +249,12 @@
       <b/>
       <i/>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -345,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -386,6 +403,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -808,29 +828,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="18" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" s="11" customFormat="1" ht="391.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="326.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="10"/>
@@ -838,7 +858,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" ht="371" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="315" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
@@ -846,10 +866,12 @@
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="18" t="s">
+        <v>28</v>
+      </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
